--- a/resources/TPG_Input/TPG_UAT.xlsx
+++ b/resources/TPG_Input/TPG_UAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PulagantH\Documents\TPG-FINAL-1\resources\TPG_Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sureshd\Desktop\TPG-FINAL-1\resources\TPG_Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA98D38-0AB4-467B-8F37-58DF80BC5F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700B5D65-BF9B-4945-AB4D-BADFA85CEF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F3DB4F5-B675-45EC-9C83-DD22C3D20F32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4F3DB4F5-B675-45EC-9C83-DD22C3D20F32}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/resources/TPG_Input/TPG_UAT.xlsx
+++ b/resources/TPG_Input/TPG_UAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sureshd\Desktop\TPG-FINAL-1\resources\TPG_Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PulagantH\Documents\TPG-FINAL-3\resources\TPG_Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700B5D65-BF9B-4945-AB4D-BADFA85CEF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B39F8E9-87CA-481E-A565-1A0273EEC92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4F3DB4F5-B675-45EC-9C83-DD22C3D20F32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F3DB4F5-B675-45EC-9C83-DD22C3D20F32}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,6 +92,24 @@
     <t>_L121</t>
   </si>
   <si>
+    <t>_LO32</t>
+  </si>
+  <si>
+    <t>_LO33</t>
+  </si>
+  <si>
+    <t>_LO44</t>
+  </si>
+  <si>
+    <t>_LO76</t>
+  </si>
+  <si>
+    <t>_LO69</t>
+  </si>
+  <si>
+    <t>_L123</t>
+  </si>
+  <si>
     <t>_LO24</t>
   </si>
   <si>
@@ -309,24 +327,6 @@
   </si>
   <si>
     <t>_L117</t>
-  </si>
-  <si>
-    <t>_LO32</t>
-  </si>
-  <si>
-    <t>_LO33</t>
-  </si>
-  <si>
-    <t>_LO44</t>
-  </si>
-  <si>
-    <t>_LO76</t>
-  </si>
-  <si>
-    <t>_LO69</t>
-  </si>
-  <si>
-    <t>_L123</t>
   </si>
 </sst>
 </file>
@@ -703,392 +703,392 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
@@ -1178,7 +1178,7 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
